--- a/qtp_pyaez/data_input/soil_inputs/barley_soil_reduction.xlsx
+++ b/qtp_pyaez/data_input/soil_inputs/barley_soil_reduction.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ming-mayhu/Desktop/毕业论文/qtp-pyaez/qtp_pyaez/data_input/soil_inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C973E63B-D314-7340-BAA0-B141C08FC1C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1310E4F7-F06D-8A4F-9C84-06158FE46B65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="28800" windowHeight="16340" xr2:uid="{14BED99B-44C8-C148-922E-610FE3C0062A}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="28800" windowHeight="17980" activeTab="3" xr2:uid="{14BED99B-44C8-C148-922E-610FE3C0062A}"/>
   </bookViews>
   <sheets>
     <sheet name="SQ1" sheetId="1" r:id="rId1"/>
@@ -825,6 +825,9 @@
       <c r="D3">
         <v>0.4</v>
       </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
@@ -839,27 +842,45 @@
       <c r="D4">
         <v>70</v>
       </c>
+      <c r="E4">
+        <v>10</v>
+      </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>9</v>
       </c>
       <c r="B5">
+        <v>8.6</v>
+      </c>
+      <c r="C5">
+        <v>8.5</v>
+      </c>
+      <c r="D5">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="E5">
+        <v>8</v>
+      </c>
+      <c r="F5">
+        <v>7.5</v>
+      </c>
+      <c r="G5">
         <v>7</v>
       </c>
-      <c r="C5">
+      <c r="H5">
         <v>6.2</v>
       </c>
-      <c r="D5">
+      <c r="I5">
         <v>5.8</v>
       </c>
-      <c r="E5">
+      <c r="J5">
         <v>5.5</v>
       </c>
-      <c r="F5">
+      <c r="K5">
         <v>5</v>
       </c>
-      <c r="G5">
+      <c r="L5">
         <v>4.4000000000000004</v>
       </c>
     </row>
@@ -868,21 +889,36 @@
         <v>10</v>
       </c>
       <c r="B6">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="C6">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="D6">
         <v>70</v>
       </c>
       <c r="E6">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="F6">
+        <v>100</v>
+      </c>
+      <c r="G6">
+        <v>100</v>
+      </c>
+      <c r="H6">
+        <v>90</v>
+      </c>
+      <c r="I6">
+        <v>70</v>
+      </c>
+      <c r="J6">
+        <v>50</v>
+      </c>
+      <c r="K6">
         <v>30</v>
       </c>
-      <c r="G6">
+      <c r="L6">
         <v>10</v>
       </c>
     </row>
@@ -1042,13 +1078,17 @@
         <v>13</v>
       </c>
       <c r="B3" s="1">
+        <v>80</v>
+      </c>
+      <c r="C3" s="1">
+        <v>50</v>
+      </c>
+      <c r="D3" s="1">
+        <v>35</v>
+      </c>
+      <c r="E3" s="1">
         <v>0</v>
       </c>
-      <c r="C3" s="1">
-        <v>100</v>
-      </c>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
       <c r="F3" s="1"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.2">
@@ -1059,29 +1099,33 @@
         <v>100</v>
       </c>
       <c r="C4" s="1">
-        <v>100</v>
-      </c>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
+        <v>90</v>
+      </c>
+      <c r="D4" s="1">
+        <v>70</v>
+      </c>
+      <c r="E4" s="1">
+        <v>50</v>
+      </c>
       <c r="F4" s="1"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>15</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="1">
         <v>9</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="1">
         <v>7</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="1">
         <v>4</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="1">
         <v>2</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1089,19 +1133,19 @@
       <c r="A6" t="s">
         <v>16</v>
       </c>
-      <c r="B6">
-        <v>100</v>
-      </c>
-      <c r="C6">
+      <c r="B6" s="1">
+        <v>100</v>
+      </c>
+      <c r="C6" s="1">
         <v>90</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="1">
         <v>70</v>
       </c>
-      <c r="E6">
-        <v>50</v>
-      </c>
-      <c r="F6">
+      <c r="E6" s="1">
+        <v>50</v>
+      </c>
+      <c r="F6" s="1">
         <v>30</v>
       </c>
     </row>
@@ -1110,40 +1154,90 @@
         <v>9</v>
       </c>
       <c r="B7" s="1">
+        <v>8.6</v>
+      </c>
+      <c r="C7" s="1">
+        <v>8.5</v>
+      </c>
+      <c r="D7" s="1">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="E7" s="1">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="F7" s="1">
+        <v>7.5</v>
+      </c>
+      <c r="G7" s="1">
         <v>7</v>
       </c>
-      <c r="C7" s="1">
-        <v>0</v>
-      </c>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
+      <c r="H7" s="1">
+        <v>6.2</v>
+      </c>
+      <c r="I7" s="1">
+        <v>5.8</v>
+      </c>
+      <c r="J7" s="1">
+        <v>5.5</v>
+      </c>
+      <c r="K7" s="1">
+        <v>4.95</v>
+      </c>
+      <c r="L7" s="1">
+        <v>4.4000000000000004</v>
+      </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>10</v>
       </c>
       <c r="B8" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="C8" s="1">
-        <v>100</v>
-      </c>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
+        <v>50</v>
+      </c>
+      <c r="D8" s="1">
+        <v>70</v>
+      </c>
+      <c r="E8" s="1">
+        <v>90</v>
+      </c>
+      <c r="F8" s="1">
+        <v>100</v>
+      </c>
+      <c r="G8" s="1">
+        <v>100</v>
+      </c>
+      <c r="H8" s="1">
+        <v>90</v>
+      </c>
+      <c r="I8" s="1">
+        <v>70</v>
+      </c>
+      <c r="J8" s="1">
+        <v>50</v>
+      </c>
+      <c r="K8" s="1">
+        <v>30</v>
+      </c>
+      <c r="L8" s="1">
+        <v>10</v>
+      </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="1">
+        <v>24</v>
+      </c>
+      <c r="C9" s="1">
+        <v>16</v>
+      </c>
+      <c r="D9" s="1">
         <v>0</v>
       </c>
-      <c r="C9" s="1">
-        <v>100</v>
-      </c>
-      <c r="D9" s="1"/>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
     </row>
@@ -1155,9 +1249,11 @@
         <v>100</v>
       </c>
       <c r="C10" s="1">
-        <v>100</v>
-      </c>
-      <c r="D10" s="1"/>
+        <v>90</v>
+      </c>
+      <c r="D10" s="1">
+        <v>70</v>
+      </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
     </row>
